--- a/automation/reports/excel/Passed_Test_Cases.xlsx
+++ b/automation/reports/excel/Passed_Test_Cases.xlsx
@@ -447,7 +447,7 @@
         <v>High</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v>High</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         <v>Medium</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v>Medium</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/automation/reports/excel/Passed_Test_Cases.xlsx
+++ b/automation/reports/excel/Passed_Test_Cases.xlsx
@@ -430,7 +430,7 @@
         <v>High</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -481,7 +481,7 @@
         <v>High</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         <v>Medium</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v>Medium</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
